--- a/erp-server/erp-server-file/src/main/resources/excel/workflow/process_management.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/workflow/process_management.xlsx
@@ -4,19 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>流程名称</t>
   </si>
@@ -24,6 +35,9 @@
     <t>单据名称</t>
   </si>
   <si>
+    <t>单据单号</t>
+  </si>
+  <si>
     <t>流程版本</t>
   </si>
   <si>
@@ -33,18 +47,27 @@
     <t>最新审核人</t>
   </si>
   <si>
-    <t>状态</t>
+    <t>流程状态</t>
+  </si>
+  <si>
+    <t>审核来源</t>
   </si>
   <si>
     <t>创建时间</t>
   </si>
   <si>
+    <t>完成审核时间</t>
+  </si>
+  <si>
     <t>{.processName}</t>
   </si>
   <si>
     <t>{.businessName}</t>
   </si>
   <si>
+    <t>{.businessCode}</t>
+  </si>
+  <si>
     <t>{.processVersion}</t>
   </si>
   <si>
@@ -57,13 +80,19 @@
     <t>{.processStatusName}</t>
   </si>
   <si>
+    <t>{.sourcePlatformName}</t>
+  </si>
+  <si>
     <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.approveTime}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1068,19 +1097,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="24.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.375" style="2" customWidth="1"/>
+    <col min="3" max="4" width="26.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.875" style="2" customWidth="1"/>
+    <col min="8" max="10" width="17.375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1102,28 +1131,46 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1131,26 +1178,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/workflow/process_management.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/workflow/process_management.xlsx
@@ -62,7 +62,7 @@
     <t>{.processName}</t>
   </si>
   <si>
-    <t>{.businessName}</t>
+    <t>{.businessKeyName}</t>
   </si>
   <si>
     <t>{.businessCode}</t>
